--- a/nr-update-smart-card/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/nr-update-smart-card/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13705" uniqueCount="1047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13705" uniqueCount="1046">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T12:44:27+00:00</t>
+    <t>2025-03-18T12:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1277,9 +1277,6 @@
   </si>
   <si>
     <t>oppositionDate</t>
-  </si>
-  <si>
-    <t>CarteProfessionnel.dateOpposition</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-smartcard.extension:oppositionDate.id</t>
@@ -18517,7 +18514,7 @@
         <v>85</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>84</v>
@@ -18619,7 +18616,7 @@
         <v>84</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>84</v>
@@ -18636,7 +18633,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>238</v>
@@ -18769,7 +18766,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>240</v>
@@ -18902,7 +18899,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>242</v>
@@ -19037,7 +19034,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>248</v>
@@ -19170,7 +19167,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>319</v>
@@ -19213,7 +19210,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>84</v>
@@ -19305,7 +19302,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>322</v>
@@ -19438,13 +19435,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>215</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>84</v>
@@ -19466,13 +19463,13 @@
         <v>84</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -19573,10 +19570,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -19602,16 +19599,16 @@
         <v>123</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>84</v>
@@ -19660,7 +19657,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>85</v>
@@ -19710,10 +19707,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -19736,17 +19733,17 @@
         <v>103</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -19783,10 +19780,10 @@
         <v>84</v>
       </c>
       <c r="AB121" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AC121" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>84</v>
@@ -19795,7 +19792,7 @@
         <v>129</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>85</v>
@@ -19831,24 +19828,24 @@
         <v>84</v>
       </c>
       <c r="AR121" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AS121" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AS121" t="s" s="2">
+      <c r="AT121" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AT121" t="s" s="2">
+      <c r="AU121" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AU121" t="s" s="2">
-        <v>436</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -19978,10 +19975,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -20113,10 +20110,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -20142,16 +20139,16 @@
         <v>191</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -20179,28 +20176,28 @@
         <v>252</v>
       </c>
       <c r="Y124" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z124" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="Z124" t="s" s="2">
+      <c r="AA124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF124" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>85</v>
@@ -20239,7 +20236,7 @@
         <v>214</v>
       </c>
       <c r="AS124" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AT124" t="s" s="2">
         <v>84</v>
@@ -20250,10 +20247,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -20279,16 +20276,16 @@
         <v>249</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -20317,25 +20314,25 @@
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF125" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>85</v>
@@ -20371,10 +20368,10 @@
         <v>84</v>
       </c>
       <c r="AR125" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AS125" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AT125" t="s" s="2">
         <v>84</v>
@@ -20385,10 +20382,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -20518,10 +20515,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -20653,10 +20650,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -20682,16 +20679,16 @@
         <v>169</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -20740,7 +20737,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>85</v>
@@ -20776,10 +20773,10 @@
         <v>84</v>
       </c>
       <c r="AR128" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS128" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AS128" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AT128" t="s" s="2">
         <v>84</v>
@@ -20790,10 +20787,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -20923,10 +20920,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -21058,10 +21055,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -21087,16 +21084,16 @@
         <v>149</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -21109,43 +21106,43 @@
         <v>84</v>
       </c>
       <c r="T131" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF131" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>85</v>
@@ -21181,10 +21178,10 @@
         <v>84</v>
       </c>
       <c r="AR131" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AS131" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AS131" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AT131" t="s" s="2">
         <v>84</v>
@@ -21195,10 +21192,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -21224,13 +21221,13 @@
         <v>116</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -21280,7 +21277,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>85</v>
@@ -21316,10 +21313,10 @@
         <v>84</v>
       </c>
       <c r="AR132" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AS132" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AS132" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="AT132" t="s" s="2">
         <v>84</v>
@@ -21330,10 +21327,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -21359,14 +21356,14 @@
         <v>191</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -21415,7 +21412,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>85</v>
@@ -21451,10 +21448,10 @@
         <v>84</v>
       </c>
       <c r="AR133" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AS133" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AS133" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AT133" t="s" s="2">
         <v>84</v>
@@ -21465,10 +21462,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -21494,14 +21491,14 @@
         <v>116</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -21550,7 +21547,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>85</v>
@@ -21586,10 +21583,10 @@
         <v>84</v>
       </c>
       <c r="AR134" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AS134" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AS134" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AT134" t="s" s="2">
         <v>84</v>
@@ -21600,10 +21597,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -21629,16 +21626,16 @@
         <v>317</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>84</v>
@@ -21687,7 +21684,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>85</v>
@@ -21723,10 +21720,10 @@
         <v>84</v>
       </c>
       <c r="AR135" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AS135" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AS135" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AT135" t="s" s="2">
         <v>84</v>
@@ -21737,10 +21734,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -21766,16 +21763,16 @@
         <v>116</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>84</v>
@@ -21824,7 +21821,7 @@
         <v>84</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>85</v>
@@ -21860,10 +21857,10 @@
         <v>84</v>
       </c>
       <c r="AR136" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AS136" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AS136" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AT136" t="s" s="2">
         <v>84</v>
@@ -21874,10 +21871,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -21903,16 +21900,16 @@
         <v>149</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>84</v>
@@ -21925,43 +21922,43 @@
         <v>84</v>
       </c>
       <c r="T137" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF137" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>85</v>
@@ -21997,13 +21994,13 @@
         <v>84</v>
       </c>
       <c r="AR137" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AS137" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AS137" t="s" s="2">
+      <c r="AT137" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AT137" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AU137" t="s" s="2">
         <v>84</v>
@@ -22011,10 +22008,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -22040,13 +22037,13 @@
         <v>116</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -22060,43 +22057,43 @@
         <v>84</v>
       </c>
       <c r="T138" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF138" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>85</v>
@@ -22132,13 +22129,13 @@
         <v>84</v>
       </c>
       <c r="AR138" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AS138" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AS138" t="s" s="2">
+      <c r="AT138" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AT138" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="AU138" t="s" s="2">
         <v>84</v>
@@ -22146,10 +22143,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -22175,10 +22172,10 @@
         <v>269</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -22229,7 +22226,7 @@
         <v>84</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>85</v>
@@ -22265,13 +22262,13 @@
         <v>84</v>
       </c>
       <c r="AR139" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AS139" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AS139" t="s" s="2">
+      <c r="AT139" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AT139" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AU139" t="s" s="2">
         <v>84</v>
@@ -22279,10 +22276,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -22305,16 +22302,16 @@
         <v>103</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -22364,7 +22361,7 @@
         <v>84</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>85</v>
@@ -22400,13 +22397,13 @@
         <v>84</v>
       </c>
       <c r="AR140" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AS140" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AS140" t="s" s="2">
+      <c r="AT140" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AT140" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AU140" t="s" s="2">
         <v>84</v>
@@ -22414,13 +22411,13 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C141" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>84</v>
@@ -22442,17 +22439,17 @@
         <v>103</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>84</v>
@@ -22501,7 +22498,7 @@
         <v>84</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>85</v>
@@ -22528,7 +22525,7 @@
         <v>84</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AP141" t="s" s="2">
         <v>84</v>
@@ -22537,24 +22534,24 @@
         <v>84</v>
       </c>
       <c r="AR141" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AS141" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AS141" t="s" s="2">
+      <c r="AT141" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AT141" t="s" s="2">
+      <c r="AU141" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AU141" t="s" s="2">
-        <v>436</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -22684,10 +22681,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -22819,10 +22816,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -22848,16 +22845,16 @@
         <v>191</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>84</v>
@@ -22885,28 +22882,28 @@
         <v>252</v>
       </c>
       <c r="Y144" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z144" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="Z144" t="s" s="2">
+      <c r="AA144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF144" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>85</v>
@@ -22945,7 +22942,7 @@
         <v>214</v>
       </c>
       <c r="AS144" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AT144" t="s" s="2">
         <v>84</v>
@@ -22956,10 +22953,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -22985,16 +22982,16 @@
         <v>249</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="M145" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N145" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="N145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>84</v>
@@ -23004,7 +23001,7 @@
         <v>84</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>84</v>
@@ -23022,11 +23019,11 @@
         <v>173</v>
       </c>
       <c r="Y145" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z145" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="Z145" t="s" s="2">
-        <v>560</v>
-      </c>
       <c r="AA145" t="s" s="2">
         <v>84</v>
       </c>
@@ -23043,7 +23040,7 @@
         <v>84</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>85</v>
@@ -23079,10 +23076,10 @@
         <v>84</v>
       </c>
       <c r="AR145" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AS145" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AT145" t="s" s="2">
         <v>84</v>
@@ -23093,10 +23090,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -23122,16 +23119,16 @@
         <v>149</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N146" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O146" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>84</v>
@@ -23141,46 +23138,46 @@
         <v>84</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="T146" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF146" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="U146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>85</v>
@@ -23216,13 +23213,13 @@
         <v>84</v>
       </c>
       <c r="AR146" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AS146" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AS146" t="s" s="2">
+      <c r="AT146" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AT146" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AU146" t="s" s="2">
         <v>84</v>
@@ -23230,10 +23227,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -23259,13 +23256,13 @@
         <v>116</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="M147" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -23279,43 +23276,43 @@
         <v>84</v>
       </c>
       <c r="T147" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF147" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>85</v>
@@ -23351,13 +23348,13 @@
         <v>84</v>
       </c>
       <c r="AR147" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AS147" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AS147" t="s" s="2">
+      <c r="AT147" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AT147" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="AU147" t="s" s="2">
         <v>84</v>
@@ -23365,10 +23362,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -23394,10 +23391,10 @@
         <v>269</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -23448,7 +23445,7 @@
         <v>84</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>85</v>
@@ -23484,13 +23481,13 @@
         <v>84</v>
       </c>
       <c r="AR148" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AS148" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AS148" t="s" s="2">
+      <c r="AT148" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AT148" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AU148" t="s" s="2">
         <v>84</v>
@@ -23498,10 +23495,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -23524,16 +23521,16 @@
         <v>103</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L149" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -23583,7 +23580,7 @@
         <v>84</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>85</v>
@@ -23619,13 +23616,13 @@
         <v>84</v>
       </c>
       <c r="AR149" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AS149" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AS149" t="s" s="2">
+      <c r="AT149" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AT149" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AU149" t="s" s="2">
         <v>84</v>
@@ -23633,13 +23630,13 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C150" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C150" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>84</v>
@@ -23661,17 +23658,17 @@
         <v>103</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>84</v>
@@ -23720,7 +23717,7 @@
         <v>84</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>85</v>
@@ -23747,7 +23744,7 @@
         <v>84</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AP150" t="s" s="2">
         <v>84</v>
@@ -23756,24 +23753,24 @@
         <v>84</v>
       </c>
       <c r="AR150" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AS150" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AS150" t="s" s="2">
+      <c r="AT150" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AT150" t="s" s="2">
+      <c r="AU150" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AU150" t="s" s="2">
-        <v>436</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -23903,10 +23900,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -24038,10 +24035,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -24067,16 +24064,16 @@
         <v>191</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>84</v>
@@ -24104,28 +24101,28 @@
         <v>252</v>
       </c>
       <c r="Y153" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z153" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="Z153" t="s" s="2">
+      <c r="AA153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF153" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>85</v>
@@ -24164,7 +24161,7 @@
         <v>214</v>
       </c>
       <c r="AS153" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AT153" t="s" s="2">
         <v>84</v>
@@ -24175,10 +24172,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -24204,16 +24201,16 @@
         <v>249</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="M154" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N154" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="N154" t="s" s="2">
+      <c r="O154" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>84</v>
@@ -24223,7 +24220,7 @@
         <v>84</v>
       </c>
       <c r="S154" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="T154" t="s" s="2">
         <v>84</v>
@@ -24241,11 +24238,11 @@
         <v>173</v>
       </c>
       <c r="Y154" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z154" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="Z154" t="s" s="2">
-        <v>560</v>
-      </c>
       <c r="AA154" t="s" s="2">
         <v>84</v>
       </c>
@@ -24262,7 +24259,7 @@
         <v>84</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>85</v>
@@ -24298,10 +24295,10 @@
         <v>84</v>
       </c>
       <c r="AR154" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AS154" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AT154" t="s" s="2">
         <v>84</v>
@@ -24312,10 +24309,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -24341,16 +24338,16 @@
         <v>149</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N155" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O155" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>84</v>
@@ -24360,46 +24357,46 @@
         <v>84</v>
       </c>
       <c r="S155" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="T155" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF155" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>85</v>
@@ -24435,13 +24432,13 @@
         <v>84</v>
       </c>
       <c r="AR155" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AS155" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AS155" t="s" s="2">
+      <c r="AT155" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AT155" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AU155" t="s" s="2">
         <v>84</v>
@@ -24449,10 +24446,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -24478,13 +24475,13 @@
         <v>116</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -24498,43 +24495,43 @@
         <v>84</v>
       </c>
       <c r="T156" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF156" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>85</v>
@@ -24570,13 +24567,13 @@
         <v>84</v>
       </c>
       <c r="AR156" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AS156" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AS156" t="s" s="2">
+      <c r="AT156" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AT156" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="AU156" t="s" s="2">
         <v>84</v>
@@ -24584,10 +24581,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -24613,10 +24610,10 @@
         <v>269</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -24667,7 +24664,7 @@
         <v>84</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>85</v>
@@ -24703,13 +24700,13 @@
         <v>84</v>
       </c>
       <c r="AR157" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AS157" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AS157" t="s" s="2">
+      <c r="AT157" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AT157" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AU157" t="s" s="2">
         <v>84</v>
@@ -24717,10 +24714,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -24743,16 +24740,16 @@
         <v>103</v>
       </c>
       <c r="K158" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L158" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L158" t="s" s="2">
+      <c r="M158" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -24802,7 +24799,7 @@
         <v>84</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>85</v>
@@ -24838,13 +24835,13 @@
         <v>84</v>
       </c>
       <c r="AR158" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AS158" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AS158" t="s" s="2">
+      <c r="AT158" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AT158" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AU158" t="s" s="2">
         <v>84</v>
@@ -24852,13 +24849,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C159" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>84</v>
@@ -24880,17 +24877,17 @@
         <v>103</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>84</v>
@@ -24939,7 +24936,7 @@
         <v>84</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>85</v>
@@ -24975,24 +24972,24 @@
         <v>84</v>
       </c>
       <c r="AR159" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AS159" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AS159" t="s" s="2">
+      <c r="AT159" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AT159" t="s" s="2">
+      <c r="AU159" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AU159" t="s" s="2">
-        <v>436</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -25122,10 +25119,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -25257,10 +25254,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -25286,16 +25283,16 @@
         <v>191</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="N162" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N162" t="s" s="2">
+      <c r="O162" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>84</v>
@@ -25323,28 +25320,28 @@
         <v>252</v>
       </c>
       <c r="Y162" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z162" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="Z162" t="s" s="2">
+      <c r="AA162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF162" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF162" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>85</v>
@@ -25383,7 +25380,7 @@
         <v>214</v>
       </c>
       <c r="AS162" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AT162" t="s" s="2">
         <v>84</v>
@@ -25394,10 +25391,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -25423,16 +25420,16 @@
         <v>249</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="M163" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N163" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="N163" t="s" s="2">
+      <c r="O163" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>84</v>
@@ -25442,7 +25439,7 @@
         <v>84</v>
       </c>
       <c r="S163" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="T163" t="s" s="2">
         <v>84</v>
@@ -25460,11 +25457,11 @@
         <v>173</v>
       </c>
       <c r="Y163" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z163" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="Z163" t="s" s="2">
-        <v>560</v>
-      </c>
       <c r="AA163" t="s" s="2">
         <v>84</v>
       </c>
@@ -25481,7 +25478,7 @@
         <v>84</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>85</v>
@@ -25517,10 +25514,10 @@
         <v>84</v>
       </c>
       <c r="AR163" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AS163" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AT163" t="s" s="2">
         <v>84</v>
@@ -25531,10 +25528,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -25560,16 +25557,16 @@
         <v>149</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N164" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O164" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>84</v>
@@ -25579,46 +25576,46 @@
         <v>84</v>
       </c>
       <c r="S164" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="T164" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="U164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF164" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="U164" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V164" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W164" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X164" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z164" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA164" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB164" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD164" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE164" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF164" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>85</v>
@@ -25654,13 +25651,13 @@
         <v>84</v>
       </c>
       <c r="AR164" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AS164" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AS164" t="s" s="2">
+      <c r="AT164" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AT164" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AU164" t="s" s="2">
         <v>84</v>
@@ -25668,10 +25665,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -25697,13 +25694,13 @@
         <v>116</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -25717,43 +25714,43 @@
         <v>84</v>
       </c>
       <c r="T165" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="U165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF165" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="U165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE165" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF165" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>85</v>
@@ -25789,13 +25786,13 @@
         <v>84</v>
       </c>
       <c r="AR165" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AS165" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AS165" t="s" s="2">
+      <c r="AT165" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AT165" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="AU165" t="s" s="2">
         <v>84</v>
@@ -25803,10 +25800,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -25832,10 +25829,10 @@
         <v>269</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -25886,7 +25883,7 @@
         <v>84</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>85</v>
@@ -25922,13 +25919,13 @@
         <v>84</v>
       </c>
       <c r="AR166" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AS166" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AS166" t="s" s="2">
+      <c r="AT166" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AT166" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AU166" t="s" s="2">
         <v>84</v>
@@ -25936,10 +25933,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -25962,16 +25959,16 @@
         <v>103</v>
       </c>
       <c r="K167" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L167" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L167" t="s" s="2">
+      <c r="M167" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -26021,7 +26018,7 @@
         <v>84</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>85</v>
@@ -26057,13 +26054,13 @@
         <v>84</v>
       </c>
       <c r="AR167" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AS167" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AS167" t="s" s="2">
+      <c r="AT167" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AT167" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AU167" t="s" s="2">
         <v>84</v>
@@ -26071,10 +26068,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -26100,23 +26097,23 @@
         <v>317</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="N168" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="O168" t="s" s="2">
+      <c r="P168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q168" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="P168" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q168" t="s" s="2">
-        <v>601</v>
-      </c>
       <c r="R168" t="s" s="2">
         <v>84</v>
       </c>
@@ -26160,7 +26157,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>85</v>
@@ -26199,21 +26196,21 @@
         <v>84</v>
       </c>
       <c r="AS168" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AT168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU168" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AT168" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU168" t="s" s="2">
-        <v>603</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -26236,19 +26233,19 @@
         <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L169" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="L169" t="s" s="2">
+      <c r="M169" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="N169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>84</v>
@@ -26297,7 +26294,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>85</v>
@@ -26333,13 +26330,13 @@
         <v>84</v>
       </c>
       <c r="AR169" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AS169" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="AS169" t="s" s="2">
+      <c r="AT169" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AT169" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AU169" t="s" s="2">
         <v>84</v>
@@ -26347,10 +26344,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -26480,10 +26477,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -26615,13 +26612,13 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C172" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C172" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>84</v>
@@ -26643,13 +26640,13 @@
         <v>84</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="L172" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="M172" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -26750,10 +26747,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -26779,16 +26776,16 @@
         <v>191</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="N173" t="s" s="2">
+      <c r="O173" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="O173" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>84</v>
@@ -26817,25 +26814,25 @@
       </c>
       <c r="Y173" s="2"/>
       <c r="Z173" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF173" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="AA173" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB173" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC173" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD173" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE173" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF173" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>85</v>
@@ -26871,13 +26868,13 @@
         <v>84</v>
       </c>
       <c r="AR173" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AS173" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="AS173" t="s" s="2">
+      <c r="AT173" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AT173" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="AU173" t="s" s="2">
         <v>84</v>
@@ -26885,10 +26882,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -26914,16 +26911,16 @@
         <v>116</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="N174" t="s" s="2">
+      <c r="O174" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>84</v>
@@ -26972,7 +26969,7 @@
         <v>84</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>85</v>
@@ -27008,10 +27005,10 @@
         <v>84</v>
       </c>
       <c r="AR174" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AS174" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AS174" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AT174" t="s" s="2">
         <v>84</v>
@@ -27022,14 +27019,14 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -27051,13 +27048,13 @@
         <v>116</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -27107,7 +27104,7 @@
         <v>84</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>85</v>
@@ -27125,31 +27122,31 @@
         <v>84</v>
       </c>
       <c r="AL175" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AM175" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN175" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO175" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP175" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ175" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR175" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="AM175" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN175" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO175" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP175" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ175" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR175" t="s" s="2">
+      <c r="AS175" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="AS175" t="s" s="2">
+      <c r="AT175" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="AT175" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="AU175" t="s" s="2">
         <v>84</v>
@@ -27157,14 +27154,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -27186,13 +27183,13 @@
         <v>116</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -27242,7 +27239,7 @@
         <v>84</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>85</v>
@@ -27260,31 +27257,31 @@
         <v>84</v>
       </c>
       <c r="AL176" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AM176" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN176" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO176" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP176" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ176" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR176" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="AM176" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN176" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO176" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP176" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ176" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR176" t="s" s="2">
+      <c r="AS176" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="AS176" t="s" s="2">
+      <c r="AT176" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="AT176" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="AU176" t="s" s="2">
         <v>84</v>
@@ -27292,10 +27289,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -27321,10 +27318,10 @@
         <v>116</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -27354,28 +27351,28 @@
         <v>173</v>
       </c>
       <c r="Y177" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="Z177" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="Z177" t="s" s="2">
+      <c r="AA177" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB177" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD177" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE177" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF177" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="AA177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF177" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>85</v>
@@ -27411,13 +27408,13 @@
         <v>84</v>
       </c>
       <c r="AR177" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AS177" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="AS177" t="s" s="2">
+      <c r="AT177" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="AT177" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="AU177" t="s" s="2">
         <v>84</v>
@@ -27425,10 +27422,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -27454,10 +27451,10 @@
         <v>116</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M178" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -27487,28 +27484,28 @@
         <v>173</v>
       </c>
       <c r="Y178" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="Z178" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="Z178" t="s" s="2">
+      <c r="AA178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF178" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="AA178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF178" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>85</v>
@@ -27526,28 +27523,28 @@
         <v>84</v>
       </c>
       <c r="AL178" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AM178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR178" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="AM178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR178" t="s" s="2">
+      <c r="AS178" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="AS178" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="AT178" t="s" s="2">
         <v>84</v>
@@ -27558,10 +27555,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -27587,14 +27584,14 @@
         <v>269</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M179" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>84</v>
@@ -27643,7 +27640,7 @@
         <v>84</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>85</v>
@@ -27679,13 +27676,13 @@
         <v>84</v>
       </c>
       <c r="AR179" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AS179" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="AS179" t="s" s="2">
-        <v>682</v>
-      </c>
       <c r="AT179" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AU179" t="s" s="2">
         <v>84</v>
@@ -27693,10 +27690,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -27719,19 +27716,19 @@
         <v>84</v>
       </c>
       <c r="K180" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="L180" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="L180" t="s" s="2">
+      <c r="M180" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="N180" t="s" s="2">
+      <c r="O180" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>84</v>
@@ -27768,17 +27765,17 @@
         <v>84</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AC180" s="2"/>
       <c r="AD180" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>85</v>
@@ -27790,37 +27787,37 @@
         <v>224</v>
       </c>
       <c r="AJ180" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AK180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO180" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="AK180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO180" t="s" s="2">
+      <c r="AP180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR180" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="AP180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR180" t="s" s="2">
+      <c r="AS180" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="AS180" t="s" s="2">
+      <c r="AT180" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="AT180" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="AU180" t="s" s="2">
         <v>84</v>
@@ -27828,13 +27825,13 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="C181" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="D181" t="s" s="2">
         <v>84</v>
@@ -27856,19 +27853,19 @@
         <v>84</v>
       </c>
       <c r="K181" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L181" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="L181" t="s" s="2">
-        <v>699</v>
-      </c>
       <c r="M181" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N181" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="N181" t="s" s="2">
+      <c r="O181" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>84</v>
@@ -27917,7 +27914,7 @@
         <v>84</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>85</v>
@@ -27929,13 +27926,13 @@
         <v>224</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AM181" t="s" s="2">
         <v>84</v>
@@ -27953,13 +27950,13 @@
         <v>84</v>
       </c>
       <c r="AR181" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AS181" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="AS181" t="s" s="2">
+      <c r="AT181" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="AT181" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="AU181" t="s" s="2">
         <v>84</v>
@@ -27967,10 +27964,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="B182" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>702</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -28100,10 +28097,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="B183" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -28233,13 +28230,13 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C184" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="C184" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="D184" t="s" s="2">
         <v>84</v>
@@ -28261,13 +28258,13 @@
         <v>84</v>
       </c>
       <c r="K184" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="L184" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="L184" t="s" s="2">
+      <c r="M184" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -28368,10 +28365,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="B185" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -28501,10 +28498,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="B186" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -28634,10 +28631,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="B187" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -28677,7 +28674,7 @@
       </c>
       <c r="Q187" s="2"/>
       <c r="R187" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="S187" t="s" s="2">
         <v>84</v>
@@ -28769,10 +28766,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="B188" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -28813,7 +28810,7 @@
         <v>84</v>
       </c>
       <c r="S188" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="T188" t="s" s="2">
         <v>84</v>
@@ -28832,7 +28829,7 @@
       </c>
       <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>84</v>
@@ -28900,13 +28897,13 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C189" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="C189" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>84</v>
@@ -28928,13 +28925,13 @@
         <v>84</v>
       </c>
       <c r="K189" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="L189" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="L189" t="s" s="2">
+      <c r="M189" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -29035,10 +29032,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -29168,10 +29165,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -29303,10 +29300,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C192" t="s" s="2">
         <v>332</v>
@@ -29334,7 +29331,7 @@
         <v>123</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="M192" t="s" s="2">
         <v>217</v>
@@ -29438,10 +29435,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="B193" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -29571,10 +29568,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -29704,10 +29701,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="B195" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -29839,10 +29836,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="B196" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -29902,7 +29899,7 @@
       </c>
       <c r="Y196" s="2"/>
       <c r="Z196" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>84</v>
@@ -29970,13 +29967,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C197" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C197" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>84</v>
@@ -30105,10 +30102,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -30238,10 +30235,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -30371,10 +30368,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -30414,7 +30411,7 @@
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="S200" t="s" s="2">
         <v>84</v>
@@ -30506,10 +30503,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -30639,13 +30636,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C202" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C202" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>84</v>
@@ -30774,10 +30771,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -30907,10 +30904,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -31040,10 +31037,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -31083,7 +31080,7 @@
       </c>
       <c r="Q205" s="2"/>
       <c r="R205" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="S205" t="s" s="2">
         <v>84</v>
@@ -31175,10 +31172,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -31308,13 +31305,13 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C207" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="B207" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C207" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="D207" t="s" s="2">
         <v>84</v>
@@ -31443,10 +31440,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -31576,10 +31573,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -31709,10 +31706,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -31752,7 +31749,7 @@
       </c>
       <c r="Q210" s="2"/>
       <c r="R210" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="S210" t="s" s="2">
         <v>84</v>
@@ -31844,10 +31841,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -31977,13 +31974,13 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C212" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="B212" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C212" t="s" s="2">
-        <v>758</v>
       </c>
       <c r="D212" t="s" s="2">
         <v>84</v>
@@ -32112,10 +32109,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -32245,10 +32242,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -32378,10 +32375,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -32421,7 +32418,7 @@
       </c>
       <c r="Q215" s="2"/>
       <c r="R215" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="S215" t="s" s="2">
         <v>84</v>
@@ -32513,10 +32510,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -32646,13 +32643,13 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C217" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="B217" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C217" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="D217" t="s" s="2">
         <v>84</v>
@@ -32781,10 +32778,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -32914,10 +32911,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -33047,10 +33044,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -33090,7 +33087,7 @@
       </c>
       <c r="Q220" s="2"/>
       <c r="R220" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="S220" t="s" s="2">
         <v>84</v>
@@ -33182,10 +33179,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -33315,13 +33312,13 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C222" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="B222" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C222" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>84</v>
@@ -33450,10 +33447,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -33583,10 +33580,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -33716,10 +33713,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -33759,7 +33756,7 @@
       </c>
       <c r="Q225" s="2"/>
       <c r="R225" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="S225" t="s" s="2">
         <v>84</v>
@@ -33851,10 +33848,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -33984,10 +33981,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -34027,7 +34024,7 @@
       </c>
       <c r="Q227" s="2"/>
       <c r="R227" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="S227" t="s" s="2">
         <v>84</v>
@@ -34119,10 +34116,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -34252,10 +34249,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="B229" t="s" s="2">
         <v>778</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>779</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -34281,10 +34278,10 @@
         <v>191</v>
       </c>
       <c r="L229" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="M229" t="s" s="2">
         <v>780</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>781</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -34296,7 +34293,7 @@
         <v>84</v>
       </c>
       <c r="S229" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="T229" t="s" s="2">
         <v>84</v>
@@ -34314,37 +34311,37 @@
         <v>252</v>
       </c>
       <c r="Y229" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="Z229" t="s" s="2">
         <v>783</v>
       </c>
-      <c r="Z229" t="s" s="2">
+      <c r="AA229" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB229" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC229" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD229" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE229" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF229" t="s" s="2">
         <v>784</v>
       </c>
-      <c r="AA229" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB229" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC229" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD229" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE229" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF229" t="s" s="2">
+      <c r="AG229" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH229" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI229" t="s" s="2">
         <v>785</v>
-      </c>
-      <c r="AG229" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH229" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI229" t="s" s="2">
-        <v>786</v>
       </c>
       <c r="AJ229" t="s" s="2">
         <v>114</v>
@@ -34371,13 +34368,13 @@
         <v>84</v>
       </c>
       <c r="AR229" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AS229" t="s" s="2">
         <v>787</v>
       </c>
-      <c r="AS229" t="s" s="2">
+      <c r="AT229" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="AT229" t="s" s="2">
-        <v>789</v>
       </c>
       <c r="AU229" t="s" s="2">
         <v>84</v>
@@ -34385,10 +34382,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="B230" t="s" s="2">
         <v>790</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>791</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -34414,16 +34411,16 @@
         <v>116</v>
       </c>
       <c r="L230" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="M230" t="s" s="2">
         <v>792</v>
       </c>
-      <c r="M230" t="s" s="2">
+      <c r="N230" t="s" s="2">
         <v>793</v>
       </c>
-      <c r="N230" t="s" s="2">
+      <c r="O230" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="O230" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>84</v>
@@ -34472,7 +34469,7 @@
         <v>84</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>85</v>
@@ -34508,13 +34505,13 @@
         <v>84</v>
       </c>
       <c r="AR230" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="AS230" t="s" s="2">
         <v>797</v>
       </c>
-      <c r="AS230" t="s" s="2">
-        <v>798</v>
-      </c>
       <c r="AT230" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AU230" t="s" s="2">
         <v>84</v>
@@ -34522,10 +34519,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="B231" t="s" s="2">
         <v>799</v>
-      </c>
-      <c r="B231" t="s" s="2">
-        <v>800</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -34551,16 +34548,16 @@
         <v>191</v>
       </c>
       <c r="L231" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="M231" t="s" s="2">
         <v>801</v>
       </c>
-      <c r="M231" t="s" s="2">
+      <c r="N231" t="s" s="2">
         <v>802</v>
       </c>
-      <c r="N231" t="s" s="2">
+      <c r="O231" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="O231" t="s" s="2">
-        <v>804</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>84</v>
@@ -34588,28 +34585,28 @@
         <v>252</v>
       </c>
       <c r="Y231" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="Z231" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="Z231" t="s" s="2">
+      <c r="AA231" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB231" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC231" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD231" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE231" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF231" t="s" s="2">
         <v>806</v>
-      </c>
-      <c r="AA231" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB231" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC231" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD231" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE231" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF231" t="s" s="2">
-        <v>807</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>85</v>
@@ -34645,13 +34642,13 @@
         <v>84</v>
       </c>
       <c r="AR231" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="AS231" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AT231" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="AS231" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AT231" t="s" s="2">
-        <v>809</v>
       </c>
       <c r="AU231" t="s" s="2">
         <v>84</v>
@@ -34659,10 +34656,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="B232" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -34685,16 +34682,16 @@
         <v>103</v>
       </c>
       <c r="K232" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="L232" t="s" s="2">
         <v>812</v>
       </c>
-      <c r="L232" t="s" s="2">
+      <c r="M232" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="M232" t="s" s="2">
+      <c r="N232" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="N232" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -34744,7 +34741,7 @@
         <v>84</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>85</v>
@@ -34794,10 +34791,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B233" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -34823,10 +34820,10 @@
         <v>269</v>
       </c>
       <c r="L233" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="M233" t="s" s="2">
         <v>819</v>
-      </c>
-      <c r="M233" t="s" s="2">
-        <v>820</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -34877,7 +34874,7 @@
         <v>84</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>85</v>
@@ -34916,10 +34913,10 @@
         <v>214</v>
       </c>
       <c r="AS233" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AT233" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AU233" t="s" s="2">
         <v>84</v>
@@ -34927,10 +34924,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -34953,19 +34950,19 @@
         <v>84</v>
       </c>
       <c r="K234" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="L234" t="s" s="2">
         <v>823</v>
       </c>
-      <c r="L234" t="s" s="2">
+      <c r="M234" t="s" s="2">
         <v>824</v>
       </c>
-      <c r="M234" t="s" s="2">
+      <c r="N234" t="s" s="2">
         <v>825</v>
       </c>
-      <c r="N234" t="s" s="2">
+      <c r="O234" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="O234" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>84</v>
@@ -35014,7 +35011,7 @@
         <v>84</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>85</v>
@@ -35041,22 +35038,22 @@
         <v>84</v>
       </c>
       <c r="AO234" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="AP234" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ234" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR234" t="s" s="2">
         <v>828</v>
       </c>
-      <c r="AP234" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ234" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR234" t="s" s="2">
+      <c r="AS234" t="s" s="2">
         <v>829</v>
       </c>
-      <c r="AS234" t="s" s="2">
+      <c r="AT234" t="s" s="2">
         <v>830</v>
-      </c>
-      <c r="AT234" t="s" s="2">
-        <v>831</v>
       </c>
       <c r="AU234" t="s" s="2">
         <v>84</v>
@@ -35064,10 +35061,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -35093,14 +35090,14 @@
         <v>191</v>
       </c>
       <c r="L235" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="M235" t="s" s="2">
         <v>833</v>
-      </c>
-      <c r="M235" t="s" s="2">
-        <v>834</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>84</v>
@@ -35128,11 +35125,11 @@
         <v>252</v>
       </c>
       <c r="Y235" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="Z235" t="s" s="2">
         <v>836</v>
       </c>
-      <c r="Z235" t="s" s="2">
-        <v>837</v>
-      </c>
       <c r="AA235" t="s" s="2">
         <v>84</v>
       </c>
@@ -35149,7 +35146,7 @@
         <v>84</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>85</v>
@@ -35185,13 +35182,13 @@
         <v>84</v>
       </c>
       <c r="AR235" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="AS235" t="s" s="2">
         <v>838</v>
       </c>
-      <c r="AS235" t="s" s="2">
+      <c r="AT235" t="s" s="2">
         <v>839</v>
-      </c>
-      <c r="AT235" t="s" s="2">
-        <v>840</v>
       </c>
       <c r="AU235" t="s" s="2">
         <v>84</v>
@@ -35199,10 +35196,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -35225,17 +35222,17 @@
         <v>103</v>
       </c>
       <c r="K236" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="L236" t="s" s="2">
         <v>842</v>
       </c>
-      <c r="L236" t="s" s="2">
+      <c r="M236" t="s" s="2">
         <v>843</v>
-      </c>
-      <c r="M236" t="s" s="2">
-        <v>844</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>84</v>
@@ -35284,7 +35281,7 @@
         <v>84</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>85</v>
@@ -35320,13 +35317,13 @@
         <v>84</v>
       </c>
       <c r="AR236" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="AS236" t="s" s="2">
         <v>846</v>
       </c>
-      <c r="AS236" t="s" s="2">
+      <c r="AT236" t="s" s="2">
         <v>847</v>
-      </c>
-      <c r="AT236" t="s" s="2">
-        <v>848</v>
       </c>
       <c r="AU236" t="s" s="2">
         <v>84</v>
@@ -35334,10 +35331,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -35360,17 +35357,17 @@
         <v>84</v>
       </c>
       <c r="K237" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="L237" t="s" s="2">
         <v>850</v>
       </c>
-      <c r="L237" t="s" s="2">
+      <c r="M237" t="s" s="2">
         <v>851</v>
-      </c>
-      <c r="M237" t="s" s="2">
-        <v>852</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>84</v>
@@ -35419,7 +35416,7 @@
         <v>84</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>85</v>
@@ -35458,10 +35455,10 @@
         <v>84</v>
       </c>
       <c r="AS237" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="AT237" t="s" s="2">
         <v>854</v>
-      </c>
-      <c r="AT237" t="s" s="2">
-        <v>855</v>
       </c>
       <c r="AU237" t="s" s="2">
         <v>84</v>
@@ -35469,10 +35466,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -35495,13 +35492,13 @@
         <v>84</v>
       </c>
       <c r="K238" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="L238" t="s" s="2">
         <v>857</v>
       </c>
-      <c r="L238" t="s" s="2">
+      <c r="M238" t="s" s="2">
         <v>858</v>
-      </c>
-      <c r="M238" t="s" s="2">
-        <v>859</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -35540,7 +35537,7 @@
         <v>84</v>
       </c>
       <c r="AB238" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="AC238" s="2"/>
       <c r="AD238" t="s" s="2">
@@ -35550,7 +35547,7 @@
         <v>129</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>85</v>
@@ -35586,13 +35583,13 @@
         <v>84</v>
       </c>
       <c r="AR238" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="AS238" t="s" s="2">
         <v>861</v>
       </c>
-      <c r="AS238" t="s" s="2">
+      <c r="AT238" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="AT238" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="AU238" t="s" s="2">
         <v>84</v>
@@ -35600,10 +35597,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -35733,10 +35730,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -35868,14 +35865,14 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
@@ -35897,16 +35894,16 @@
         <v>123</v>
       </c>
       <c r="L241" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="M241" t="s" s="2">
         <v>868</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>869</v>
       </c>
       <c r="N241" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O241" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>84</v>
@@ -35955,7 +35952,7 @@
         <v>84</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>85</v>
@@ -36005,10 +36002,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -36031,17 +36028,17 @@
         <v>84</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L242" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="M242" t="s" s="2">
         <v>872</v>
-      </c>
-      <c r="M242" t="s" s="2">
-        <v>873</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>84</v>
@@ -36090,7 +36087,7 @@
         <v>84</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>85</v>
@@ -36114,22 +36111,22 @@
         <v>84</v>
       </c>
       <c r="AN242" t="s" s="2">
+        <v>874</v>
+      </c>
+      <c r="AO242" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP242" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ242" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR242" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS242" t="s" s="2">
         <v>875</v>
-      </c>
-      <c r="AO242" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP242" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ242" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR242" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS242" t="s" s="2">
-        <v>876</v>
       </c>
       <c r="AT242" t="s" s="2">
         <v>84</v>
@@ -36140,10 +36137,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -36169,10 +36166,10 @@
         <v>249</v>
       </c>
       <c r="L243" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="M243" t="s" s="2">
         <v>878</v>
-      </c>
-      <c r="M243" t="s" s="2">
-        <v>879</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" s="2"/>
@@ -36202,11 +36199,11 @@
         <v>181</v>
       </c>
       <c r="Y243" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="Z243" t="s" s="2">
         <v>880</v>
       </c>
-      <c r="Z243" t="s" s="2">
-        <v>881</v>
-      </c>
       <c r="AA243" t="s" s="2">
         <v>84</v>
       </c>
@@ -36223,7 +36220,7 @@
         <v>84</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>102</v>
@@ -36247,25 +36244,25 @@
         <v>84</v>
       </c>
       <c r="AN243" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="AO243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS243" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="AT243" t="s" s="2">
         <v>882</v>
-      </c>
-      <c r="AO243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS243" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="AT243" t="s" s="2">
-        <v>883</v>
       </c>
       <c r="AU243" t="s" s="2">
         <v>84</v>
@@ -36273,10 +36270,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -36302,14 +36299,14 @@
         <v>269</v>
       </c>
       <c r="L244" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="M244" t="s" s="2">
         <v>885</v>
-      </c>
-      <c r="M244" t="s" s="2">
-        <v>886</v>
       </c>
       <c r="N244" s="2"/>
       <c r="O244" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>84</v>
@@ -36358,7 +36355,7 @@
         <v>84</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>85</v>
@@ -36397,10 +36394,10 @@
         <v>84</v>
       </c>
       <c r="AS244" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="AT244" t="s" s="2">
         <v>888</v>
-      </c>
-      <c r="AT244" t="s" s="2">
-        <v>889</v>
       </c>
       <c r="AU244" t="s" s="2">
         <v>84</v>
@@ -36408,10 +36405,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -36434,13 +36431,13 @@
         <v>84</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L245" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="M245" t="s" s="2">
         <v>891</v>
-      </c>
-      <c r="M245" t="s" s="2">
-        <v>892</v>
       </c>
       <c r="N245" s="2"/>
       <c r="O245" s="2"/>
@@ -36491,7 +36488,7 @@
         <v>84</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>85</v>
@@ -36530,7 +36527,7 @@
         <v>84</v>
       </c>
       <c r="AS245" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AT245" t="s" s="2">
         <v>84</v>
@@ -36541,13 +36538,13 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="C246" t="s" s="2">
         <v>894</v>
-      </c>
-      <c r="B246" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="C246" t="s" s="2">
-        <v>895</v>
       </c>
       <c r="D246" t="s" s="2">
         <v>84</v>
@@ -36569,13 +36566,13 @@
         <v>84</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N246" s="2"/>
       <c r="O246" s="2"/>
@@ -36626,7 +36623,7 @@
         <v>84</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>85</v>
@@ -36650,7 +36647,7 @@
         <v>84</v>
       </c>
       <c r="AN246" t="s" s="2">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="AO246" t="s" s="2">
         <v>84</v>
@@ -36662,13 +36659,13 @@
         <v>84</v>
       </c>
       <c r="AR246" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="AS246" t="s" s="2">
         <v>861</v>
       </c>
-      <c r="AS246" t="s" s="2">
+      <c r="AT246" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="AT246" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="AU246" t="s" s="2">
         <v>84</v>
@@ -36676,10 +36673,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -36809,10 +36806,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -36940,13 +36937,13 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="C249" t="s" s="2">
         <v>900</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C249" t="s" s="2">
-        <v>901</v>
       </c>
       <c r="D249" t="s" s="2">
         <v>84</v>
@@ -36968,13 +36965,13 @@
         <v>84</v>
       </c>
       <c r="K249" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="L249" t="s" s="2">
         <v>902</v>
       </c>
-      <c r="L249" t="s" s="2">
+      <c r="M249" t="s" s="2">
         <v>903</v>
-      </c>
-      <c r="M249" t="s" s="2">
-        <v>904</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" s="2"/>
@@ -37075,10 +37072,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="B250" t="s" s="2">
         <v>905</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>906</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -37208,10 +37205,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
+        <v>906</v>
+      </c>
+      <c r="B251" t="s" s="2">
         <v>907</v>
-      </c>
-      <c r="B251" t="s" s="2">
-        <v>908</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -37343,13 +37340,13 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="C252" t="s" s="2">
         <v>909</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="C252" t="s" s="2">
-        <v>910</v>
       </c>
       <c r="D252" t="s" s="2">
         <v>84</v>
@@ -37452,7 +37449,7 @@
         <v>84</v>
       </c>
       <c r="AN252" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="AO252" t="s" s="2">
         <v>84</v>
@@ -37478,10 +37475,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="B253" t="s" s="2">
         <v>912</v>
-      </c>
-      <c r="B253" t="s" s="2">
-        <v>913</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -37611,10 +37608,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="B254" t="s" s="2">
         <v>914</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>915</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -37744,10 +37741,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="B255" t="s" s="2">
         <v>916</v>
-      </c>
-      <c r="B255" t="s" s="2">
-        <v>917</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -37787,7 +37784,7 @@
       </c>
       <c r="Q255" s="2"/>
       <c r="R255" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="S255" t="s" s="2">
         <v>84</v>
@@ -37879,10 +37876,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="B256" t="s" s="2">
         <v>918</v>
-      </c>
-      <c r="B256" t="s" s="2">
-        <v>919</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -37942,7 +37939,7 @@
       </c>
       <c r="Y256" s="2"/>
       <c r="Z256" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>84</v>
@@ -38010,13 +38007,13 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="B257" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="C257" t="s" s="2">
         <v>921</v>
-      </c>
-      <c r="B257" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="C257" t="s" s="2">
-        <v>922</v>
       </c>
       <c r="D257" t="s" s="2">
         <v>84</v>
@@ -38119,7 +38116,7 @@
         <v>84</v>
       </c>
       <c r="AN257" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="AO257" t="s" s="2">
         <v>84</v>
@@ -38145,10 +38142,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -38278,10 +38275,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -38411,10 +38408,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -38454,7 +38451,7 @@
       </c>
       <c r="Q260" s="2"/>
       <c r="R260" t="s" s="2">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="S260" t="s" s="2">
         <v>84</v>
@@ -38546,10 +38543,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -38609,7 +38606,7 @@
       </c>
       <c r="Y261" s="2"/>
       <c r="Z261" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="AA261" t="s" s="2">
         <v>84</v>
@@ -38677,13 +38674,13 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
+        <v>928</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="C262" t="s" s="2">
         <v>929</v>
-      </c>
-      <c r="B262" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="C262" t="s" s="2">
-        <v>930</v>
       </c>
       <c r="D262" t="s" s="2">
         <v>84</v>
@@ -38786,7 +38783,7 @@
         <v>84</v>
       </c>
       <c r="AN262" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="AO262" t="s" s="2">
         <v>84</v>
@@ -38812,10 +38809,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -38945,10 +38942,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -39078,10 +39075,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -39121,7 +39118,7 @@
       </c>
       <c r="Q265" s="2"/>
       <c r="R265" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="S265" t="s" s="2">
         <v>84</v>
@@ -39213,10 +39210,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -39276,7 +39273,7 @@
       </c>
       <c r="Y266" s="2"/>
       <c r="Z266" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>84</v>
@@ -39344,10 +39341,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B267" t="s" s="2">
         <v>937</v>
-      </c>
-      <c r="B267" t="s" s="2">
-        <v>938</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -39387,7 +39384,7 @@
       </c>
       <c r="Q267" s="2"/>
       <c r="R267" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="S267" t="s" s="2">
         <v>84</v>
@@ -39479,10 +39476,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
+        <v>939</v>
+      </c>
+      <c r="B268" t="s" s="2">
         <v>940</v>
-      </c>
-      <c r="B268" t="s" s="2">
-        <v>941</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -39612,14 +39609,14 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E269" s="2"/>
       <c r="F269" t="s" s="2">
@@ -39641,16 +39638,16 @@
         <v>123</v>
       </c>
       <c r="L269" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="M269" t="s" s="2">
         <v>868</v>
-      </c>
-      <c r="M269" t="s" s="2">
-        <v>869</v>
       </c>
       <c r="N269" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O269" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P269" t="s" s="2">
         <v>84</v>
@@ -39699,7 +39696,7 @@
         <v>84</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>85</v>
@@ -39749,10 +39746,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -39775,17 +39772,17 @@
         <v>84</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L270" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="M270" t="s" s="2">
         <v>872</v>
-      </c>
-      <c r="M270" t="s" s="2">
-        <v>873</v>
       </c>
       <c r="N270" s="2"/>
       <c r="O270" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="P270" t="s" s="2">
         <v>84</v>
@@ -39834,7 +39831,7 @@
         <v>84</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>85</v>
@@ -39873,7 +39870,7 @@
         <v>84</v>
       </c>
       <c r="AS270" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="AT270" t="s" s="2">
         <v>84</v>
@@ -39884,10 +39881,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -39913,10 +39910,10 @@
         <v>249</v>
       </c>
       <c r="L271" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="M271" t="s" s="2">
         <v>878</v>
-      </c>
-      <c r="M271" t="s" s="2">
-        <v>879</v>
       </c>
       <c r="N271" s="2"/>
       <c r="O271" s="2"/>
@@ -39946,11 +39943,11 @@
         <v>181</v>
       </c>
       <c r="Y271" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="Z271" t="s" s="2">
         <v>880</v>
       </c>
-      <c r="Z271" t="s" s="2">
-        <v>881</v>
-      </c>
       <c r="AA271" t="s" s="2">
         <v>84</v>
       </c>
@@ -39967,7 +39964,7 @@
         <v>84</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>102</v>
@@ -40006,10 +40003,10 @@
         <v>84</v>
       </c>
       <c r="AS271" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AT271" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="AU271" t="s" s="2">
         <v>84</v>
@@ -40017,10 +40014,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
+        <v>944</v>
+      </c>
+      <c r="B272" t="s" s="2">
         <v>945</v>
-      </c>
-      <c r="B272" t="s" s="2">
-        <v>946</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -40150,10 +40147,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
+        <v>946</v>
+      </c>
+      <c r="B273" t="s" s="2">
         <v>947</v>
-      </c>
-      <c r="B273" t="s" s="2">
-        <v>948</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -40285,10 +40282,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
+        <v>948</v>
+      </c>
+      <c r="B274" t="s" s="2">
         <v>949</v>
-      </c>
-      <c r="B274" t="s" s="2">
-        <v>950</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -40314,16 +40311,16 @@
         <v>169</v>
       </c>
       <c r="L274" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M274" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M274" t="s" s="2">
+      <c r="N274" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N274" t="s" s="2">
+      <c r="O274" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O274" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P274" t="s" s="2">
         <v>84</v>
@@ -40367,10 +40364,10 @@
         <v>84</v>
       </c>
       <c r="AE274" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>85</v>
@@ -40406,10 +40403,10 @@
         <v>84</v>
       </c>
       <c r="AR274" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS274" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AS274" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AT274" t="s" s="2">
         <v>84</v>
@@ -40420,13 +40417,13 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="B275" t="s" s="2">
+        <v>949</v>
+      </c>
+      <c r="C275" t="s" s="2">
         <v>951</v>
-      </c>
-      <c r="B275" t="s" s="2">
-        <v>950</v>
-      </c>
-      <c r="C275" t="s" s="2">
-        <v>952</v>
       </c>
       <c r="D275" t="s" s="2">
         <v>84</v>
@@ -40451,16 +40448,16 @@
         <v>169</v>
       </c>
       <c r="L275" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M275" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M275" t="s" s="2">
+      <c r="N275" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N275" t="s" s="2">
+      <c r="O275" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O275" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P275" t="s" s="2">
         <v>84</v>
@@ -40489,7 +40486,7 @@
       </c>
       <c r="Y275" s="2"/>
       <c r="Z275" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AA275" t="s" s="2">
         <v>84</v>
@@ -40507,7 +40504,7 @@
         <v>84</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>85</v>
@@ -40543,10 +40540,10 @@
         <v>84</v>
       </c>
       <c r="AR275" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS275" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AS275" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AT275" t="s" s="2">
         <v>84</v>
@@ -40557,13 +40554,13 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D276" t="s" s="2">
         <v>84</v>
@@ -40588,16 +40585,16 @@
         <v>169</v>
       </c>
       <c r="L276" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M276" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M276" t="s" s="2">
+      <c r="N276" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N276" t="s" s="2">
+      <c r="O276" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O276" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>84</v>
@@ -40626,7 +40623,7 @@
       </c>
       <c r="Y276" s="2"/>
       <c r="Z276" t="s" s="2">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AA276" t="s" s="2">
         <v>84</v>
@@ -40644,7 +40641,7 @@
         <v>84</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>85</v>
@@ -40680,10 +40677,10 @@
         <v>84</v>
       </c>
       <c r="AR276" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS276" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AS276" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AT276" t="s" s="2">
         <v>84</v>
@@ -40694,10 +40691,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
+        <v>955</v>
+      </c>
+      <c r="B277" t="s" s="2">
         <v>956</v>
-      </c>
-      <c r="B277" t="s" s="2">
-        <v>957</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -40723,16 +40720,16 @@
         <v>116</v>
       </c>
       <c r="L277" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M277" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M277" t="s" s="2">
+      <c r="N277" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N277" t="s" s="2">
+      <c r="O277" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O277" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P277" t="s" s="2">
         <v>84</v>
@@ -40781,7 +40778,7 @@
         <v>84</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>85</v>
@@ -40817,10 +40814,10 @@
         <v>84</v>
       </c>
       <c r="AR277" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AS277" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AS277" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AT277" t="s" s="2">
         <v>84</v>
@@ -40831,10 +40828,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -40860,14 +40857,14 @@
         <v>269</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="N278" s="2"/>
       <c r="O278" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="P278" t="s" s="2">
         <v>84</v>
@@ -40916,7 +40913,7 @@
         <v>84</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>85</v>
@@ -40955,10 +40952,10 @@
         <v>84</v>
       </c>
       <c r="AS278" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="AT278" t="s" s="2">
         <v>888</v>
-      </c>
-      <c r="AT278" t="s" s="2">
-        <v>889</v>
       </c>
       <c r="AU278" t="s" s="2">
         <v>84</v>
@@ -40966,10 +40963,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="B279" t="s" s="2">
         <v>960</v>
-      </c>
-      <c r="B279" t="s" s="2">
-        <v>961</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -41099,10 +41096,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
+        <v>961</v>
+      </c>
+      <c r="B280" t="s" s="2">
         <v>962</v>
-      </c>
-      <c r="B280" t="s" s="2">
-        <v>963</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -41234,10 +41231,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
+        <v>963</v>
+      </c>
+      <c r="B281" t="s" s="2">
         <v>964</v>
-      </c>
-      <c r="B281" t="s" s="2">
-        <v>965</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -41263,7 +41260,7 @@
         <v>276</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="M281" t="s" s="2">
         <v>278</v>
@@ -41343,7 +41340,7 @@
         <v>84</v>
       </c>
       <c r="AN281" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="AO281" t="s" s="2">
         <v>84</v>
@@ -41369,10 +41366,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="B282" t="s" s="2">
         <v>968</v>
-      </c>
-      <c r="B282" t="s" s="2">
-        <v>969</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -41398,7 +41395,7 @@
         <v>276</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="M282" t="s" s="2">
         <v>288</v>
@@ -41480,7 +41477,7 @@
         <v>84</v>
       </c>
       <c r="AN282" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="AO282" t="s" s="2">
         <v>84</v>
@@ -41506,10 +41503,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -41532,13 +41529,13 @@
         <v>84</v>
       </c>
       <c r="K283" t="s" s="2">
+        <v>972</v>
+      </c>
+      <c r="L283" t="s" s="2">
         <v>973</v>
       </c>
-      <c r="L283" t="s" s="2">
-        <v>974</v>
-      </c>
       <c r="M283" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="N283" s="2"/>
       <c r="O283" s="2"/>
@@ -41589,7 +41586,7 @@
         <v>84</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>85</v>
@@ -41613,7 +41610,7 @@
         <v>84</v>
       </c>
       <c r="AN283" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="AO283" t="s" s="2">
         <v>84</v>
@@ -41628,7 +41625,7 @@
         <v>84</v>
       </c>
       <c r="AS283" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AT283" t="s" s="2">
         <v>84</v>
@@ -41639,13 +41636,13 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="C284" t="s" s="2">
         <v>976</v>
-      </c>
-      <c r="B284" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="C284" t="s" s="2">
-        <v>977</v>
       </c>
       <c r="D284" t="s" s="2">
         <v>84</v>
@@ -41667,13 +41664,13 @@
         <v>84</v>
       </c>
       <c r="K284" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N284" s="2"/>
       <c r="O284" s="2"/>
@@ -41724,7 +41721,7 @@
         <v>84</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>85</v>
@@ -41760,13 +41757,13 @@
         <v>84</v>
       </c>
       <c r="AR284" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="AS284" t="s" s="2">
         <v>861</v>
       </c>
-      <c r="AS284" t="s" s="2">
+      <c r="AT284" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="AT284" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="AU284" t="s" s="2">
         <v>84</v>
@@ -41774,10 +41771,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -41907,10 +41904,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -42042,14 +42039,14 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E287" s="2"/>
       <c r="F287" t="s" s="2">
@@ -42071,16 +42068,16 @@
         <v>123</v>
       </c>
       <c r="L287" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="M287" t="s" s="2">
         <v>868</v>
-      </c>
-      <c r="M287" t="s" s="2">
-        <v>869</v>
       </c>
       <c r="N287" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O287" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P287" t="s" s="2">
         <v>84</v>
@@ -42129,7 +42126,7 @@
         <v>84</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>85</v>
@@ -42179,10 +42176,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -42205,17 +42202,17 @@
         <v>84</v>
       </c>
       <c r="K288" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L288" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="M288" t="s" s="2">
         <v>872</v>
-      </c>
-      <c r="M288" t="s" s="2">
-        <v>873</v>
       </c>
       <c r="N288" s="2"/>
       <c r="O288" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="P288" t="s" s="2">
         <v>84</v>
@@ -42264,7 +42261,7 @@
         <v>84</v>
       </c>
       <c r="AF288" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AG288" t="s" s="2">
         <v>85</v>
@@ -42303,7 +42300,7 @@
         <v>84</v>
       </c>
       <c r="AS288" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="AT288" t="s" s="2">
         <v>84</v>
@@ -42314,10 +42311,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -42343,10 +42340,10 @@
         <v>249</v>
       </c>
       <c r="L289" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="M289" t="s" s="2">
         <v>878</v>
-      </c>
-      <c r="M289" t="s" s="2">
-        <v>879</v>
       </c>
       <c r="N289" s="2"/>
       <c r="O289" s="2"/>
@@ -42376,11 +42373,11 @@
         <v>181</v>
       </c>
       <c r="Y289" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="Z289" t="s" s="2">
         <v>880</v>
       </c>
-      <c r="Z289" t="s" s="2">
-        <v>881</v>
-      </c>
       <c r="AA289" t="s" s="2">
         <v>84</v>
       </c>
@@ -42397,7 +42394,7 @@
         <v>84</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>102</v>
@@ -42436,10 +42433,10 @@
         <v>84</v>
       </c>
       <c r="AS289" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AT289" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="AU289" t="s" s="2">
         <v>84</v>
@@ -42447,10 +42444,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -42580,10 +42577,10 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -42715,10 +42712,10 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -42744,16 +42741,16 @@
         <v>169</v>
       </c>
       <c r="L292" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M292" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M292" t="s" s="2">
+      <c r="N292" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N292" t="s" s="2">
+      <c r="O292" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O292" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P292" t="s" s="2">
         <v>84</v>
@@ -42797,10 +42794,10 @@
         <v>84</v>
       </c>
       <c r="AE292" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AF292" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG292" t="s" s="2">
         <v>85</v>
@@ -42836,10 +42833,10 @@
         <v>84</v>
       </c>
       <c r="AR292" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS292" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AS292" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AT292" t="s" s="2">
         <v>84</v>
@@ -42850,13 +42847,13 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="B293" t="s" s="2">
+        <v>949</v>
+      </c>
+      <c r="C293" t="s" s="2">
         <v>987</v>
-      </c>
-      <c r="B293" t="s" s="2">
-        <v>950</v>
-      </c>
-      <c r="C293" t="s" s="2">
-        <v>988</v>
       </c>
       <c r="D293" t="s" s="2">
         <v>84</v>
@@ -42881,16 +42878,16 @@
         <v>169</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="M293" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N293" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N293" t="s" s="2">
+      <c r="O293" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O293" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P293" t="s" s="2">
         <v>84</v>
@@ -42919,7 +42916,7 @@
       </c>
       <c r="Y293" s="2"/>
       <c r="Z293" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>84</v>
@@ -42937,7 +42934,7 @@
         <v>84</v>
       </c>
       <c r="AF293" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG293" t="s" s="2">
         <v>85</v>
@@ -42955,7 +42952,7 @@
         <v>84</v>
       </c>
       <c r="AL293" t="s" s="2">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="AM293" t="s" s="2">
         <v>84</v>
@@ -42973,10 +42970,10 @@
         <v>84</v>
       </c>
       <c r="AR293" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS293" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AS293" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AT293" t="s" s="2">
         <v>84</v>
@@ -42987,10 +42984,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C294" t="s" s="2">
         <v>361</v>
@@ -43018,16 +43015,16 @@
         <v>169</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="M294" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N294" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N294" t="s" s="2">
+      <c r="O294" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O294" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P294" t="s" s="2">
         <v>84</v>
@@ -43074,7 +43071,7 @@
         <v>84</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>85</v>
@@ -43092,7 +43089,7 @@
         <v>84</v>
       </c>
       <c r="AL294" t="s" s="2">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AM294" t="s" s="2">
         <v>84</v>
@@ -43110,10 +43107,10 @@
         <v>84</v>
       </c>
       <c r="AR294" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS294" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AS294" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AT294" t="s" s="2">
         <v>84</v>
@@ -43124,10 +43121,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -43153,16 +43150,16 @@
         <v>116</v>
       </c>
       <c r="L295" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M295" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M295" t="s" s="2">
+      <c r="N295" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N295" t="s" s="2">
+      <c r="O295" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O295" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P295" t="s" s="2">
         <v>84</v>
@@ -43211,7 +43208,7 @@
         <v>84</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>85</v>
@@ -43247,10 +43244,10 @@
         <v>84</v>
       </c>
       <c r="AR295" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AS295" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AS295" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AT295" t="s" s="2">
         <v>84</v>
@@ -43261,10 +43258,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -43290,14 +43287,14 @@
         <v>269</v>
       </c>
       <c r="L296" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="M296" t="s" s="2">
         <v>885</v>
-      </c>
-      <c r="M296" t="s" s="2">
-        <v>886</v>
       </c>
       <c r="N296" s="2"/>
       <c r="O296" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="P296" t="s" s="2">
         <v>84</v>
@@ -43346,7 +43343,7 @@
         <v>84</v>
       </c>
       <c r="AF296" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AG296" t="s" s="2">
         <v>85</v>
@@ -43385,10 +43382,10 @@
         <v>84</v>
       </c>
       <c r="AS296" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="AT296" t="s" s="2">
         <v>888</v>
-      </c>
-      <c r="AT296" t="s" s="2">
-        <v>889</v>
       </c>
       <c r="AU296" t="s" s="2">
         <v>84</v>
@@ -43396,10 +43393,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -43529,10 +43526,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -43664,10 +43661,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -43693,7 +43690,7 @@
         <v>276</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="M299" t="s" s="2">
         <v>278</v>
@@ -43767,7 +43764,7 @@
         <v>84</v>
       </c>
       <c r="AL299" t="s" s="2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="AM299" t="s" s="2">
         <v>84</v>
@@ -43799,10 +43796,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -43828,7 +43825,7 @@
         <v>276</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="M300" t="s" s="2">
         <v>288</v>
@@ -43904,7 +43901,7 @@
         <v>84</v>
       </c>
       <c r="AL300" t="s" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="AM300" t="s" s="2">
         <v>84</v>
@@ -43936,10 +43933,10 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" t="s" s="2">
@@ -43962,13 +43959,13 @@
         <v>84</v>
       </c>
       <c r="K301" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L301" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="M301" t="s" s="2">
         <v>891</v>
-      </c>
-      <c r="M301" t="s" s="2">
-        <v>892</v>
       </c>
       <c r="N301" s="2"/>
       <c r="O301" s="2"/>
@@ -44019,7 +44016,7 @@
         <v>84</v>
       </c>
       <c r="AF301" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="AG301" t="s" s="2">
         <v>85</v>
@@ -44058,7 +44055,7 @@
         <v>84</v>
       </c>
       <c r="AS301" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AT301" t="s" s="2">
         <v>84</v>
@@ -44069,13 +44066,13 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B302" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="C302" t="s" s="2">
         <v>1006</v>
-      </c>
-      <c r="B302" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="C302" t="s" s="2">
-        <v>1007</v>
       </c>
       <c r="D302" t="s" s="2">
         <v>84</v>
@@ -44097,13 +44094,13 @@
         <v>84</v>
       </c>
       <c r="K302" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="L302" t="s" s="2">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="M302" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N302" s="2"/>
       <c r="O302" s="2"/>
@@ -44154,7 +44151,7 @@
         <v>84</v>
       </c>
       <c r="AF302" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AG302" t="s" s="2">
         <v>85</v>
@@ -44190,13 +44187,13 @@
         <v>84</v>
       </c>
       <c r="AR302" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="AS302" t="s" s="2">
         <v>861</v>
       </c>
-      <c r="AS302" t="s" s="2">
+      <c r="AT302" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="AT302" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="AU302" t="s" s="2">
         <v>84</v>
@@ -44204,10 +44201,10 @@
     </row>
     <row r="303" hidden="true">
       <c r="A303" t="s" s="2">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
@@ -44337,10 +44334,10 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
@@ -44472,14 +44469,14 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E305" s="2"/>
       <c r="F305" t="s" s="2">
@@ -44501,16 +44498,16 @@
         <v>123</v>
       </c>
       <c r="L305" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="M305" t="s" s="2">
         <v>868</v>
-      </c>
-      <c r="M305" t="s" s="2">
-        <v>869</v>
       </c>
       <c r="N305" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O305" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P305" t="s" s="2">
         <v>84</v>
@@ -44559,7 +44556,7 @@
         <v>84</v>
       </c>
       <c r="AF305" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AG305" t="s" s="2">
         <v>85</v>
@@ -44609,10 +44606,10 @@
     </row>
     <row r="306" hidden="true">
       <c r="A306" t="s" s="2">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" t="s" s="2">
@@ -44635,17 +44632,17 @@
         <v>84</v>
       </c>
       <c r="K306" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L306" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="M306" t="s" s="2">
         <v>872</v>
-      </c>
-      <c r="M306" t="s" s="2">
-        <v>873</v>
       </c>
       <c r="N306" s="2"/>
       <c r="O306" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="P306" t="s" s="2">
         <v>84</v>
@@ -44694,7 +44691,7 @@
         <v>84</v>
       </c>
       <c r="AF306" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AG306" t="s" s="2">
         <v>85</v>
@@ -44733,7 +44730,7 @@
         <v>84</v>
       </c>
       <c r="AS306" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="AT306" t="s" s="2">
         <v>84</v>
@@ -44744,10 +44741,10 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" t="s" s="2">
@@ -44773,10 +44770,10 @@
         <v>249</v>
       </c>
       <c r="L307" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="M307" t="s" s="2">
         <v>878</v>
-      </c>
-      <c r="M307" t="s" s="2">
-        <v>879</v>
       </c>
       <c r="N307" s="2"/>
       <c r="O307" s="2"/>
@@ -44806,11 +44803,11 @@
         <v>181</v>
       </c>
       <c r="Y307" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="Z307" t="s" s="2">
         <v>880</v>
       </c>
-      <c r="Z307" t="s" s="2">
-        <v>881</v>
-      </c>
       <c r="AA307" t="s" s="2">
         <v>84</v>
       </c>
@@ -44827,7 +44824,7 @@
         <v>84</v>
       </c>
       <c r="AF307" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AG307" t="s" s="2">
         <v>102</v>
@@ -44842,7 +44839,7 @@
         <v>114</v>
       </c>
       <c r="AK307" t="s" s="2">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="AL307" t="s" s="2">
         <v>84</v>
@@ -44866,10 +44863,10 @@
         <v>84</v>
       </c>
       <c r="AS307" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AT307" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="AU307" t="s" s="2">
         <v>84</v>
@@ -44877,10 +44874,10 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" t="s" s="2">
@@ -45010,10 +45007,10 @@
     </row>
     <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C309" s="2"/>
       <c r="D309" t="s" s="2">
@@ -45145,10 +45142,10 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" t="s" s="2">
@@ -45174,16 +45171,16 @@
         <v>169</v>
       </c>
       <c r="L310" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M310" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M310" t="s" s="2">
+      <c r="N310" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N310" t="s" s="2">
+      <c r="O310" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O310" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P310" t="s" s="2">
         <v>84</v>
@@ -45227,10 +45224,10 @@
         <v>84</v>
       </c>
       <c r="AE310" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AF310" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG310" t="s" s="2">
         <v>85</v>
@@ -45266,10 +45263,10 @@
         <v>84</v>
       </c>
       <c r="AR310" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS310" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AS310" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AT310" t="s" s="2">
         <v>84</v>
@@ -45280,13 +45277,13 @@
     </row>
     <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
+        <v>1017</v>
+      </c>
+      <c r="B311" t="s" s="2">
+        <v>949</v>
+      </c>
+      <c r="C311" t="s" s="2">
         <v>1018</v>
-      </c>
-      <c r="B311" t="s" s="2">
-        <v>950</v>
-      </c>
-      <c r="C311" t="s" s="2">
-        <v>1019</v>
       </c>
       <c r="D311" t="s" s="2">
         <v>84</v>
@@ -45311,16 +45308,16 @@
         <v>169</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M311" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N311" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N311" t="s" s="2">
+      <c r="O311" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O311" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P311" t="s" s="2">
         <v>84</v>
@@ -45349,7 +45346,7 @@
       </c>
       <c r="Y311" s="2"/>
       <c r="Z311" t="s" s="2">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="AA311" t="s" s="2">
         <v>84</v>
@@ -45367,7 +45364,7 @@
         <v>84</v>
       </c>
       <c r="AF311" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG311" t="s" s="2">
         <v>85</v>
@@ -45382,7 +45379,7 @@
         <v>114</v>
       </c>
       <c r="AK311" t="s" s="2">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AL311" t="s" s="2">
         <v>84</v>
@@ -45403,10 +45400,10 @@
         <v>84</v>
       </c>
       <c r="AR311" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS311" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AS311" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AT311" t="s" s="2">
         <v>84</v>
@@ -45417,13 +45414,13 @@
     </row>
     <row r="312" hidden="true">
       <c r="A312" t="s" s="2">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D312" t="s" s="2">
         <v>84</v>
@@ -45448,16 +45445,16 @@
         <v>169</v>
       </c>
       <c r="L312" t="s" s="2">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="M312" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N312" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N312" t="s" s="2">
+      <c r="O312" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O312" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P312" t="s" s="2">
         <v>84</v>
@@ -45486,7 +45483,7 @@
       </c>
       <c r="Y312" s="2"/>
       <c r="Z312" t="s" s="2">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="AA312" t="s" s="2">
         <v>84</v>
@@ -45504,7 +45501,7 @@
         <v>84</v>
       </c>
       <c r="AF312" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG312" t="s" s="2">
         <v>85</v>
@@ -45540,10 +45537,10 @@
         <v>84</v>
       </c>
       <c r="AR312" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS312" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AS312" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AT312" t="s" s="2">
         <v>84</v>
@@ -45554,10 +45551,10 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" t="s" s="2">
@@ -45583,16 +45580,16 @@
         <v>116</v>
       </c>
       <c r="L313" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M313" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M313" t="s" s="2">
+      <c r="N313" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N313" t="s" s="2">
+      <c r="O313" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O313" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P313" t="s" s="2">
         <v>84</v>
@@ -45641,7 +45638,7 @@
         <v>84</v>
       </c>
       <c r="AF313" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG313" t="s" s="2">
         <v>85</v>
@@ -45677,10 +45674,10 @@
         <v>84</v>
       </c>
       <c r="AR313" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AS313" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AS313" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AT313" t="s" s="2">
         <v>84</v>
@@ -45691,10 +45688,10 @@
     </row>
     <row r="314" hidden="true">
       <c r="A314" t="s" s="2">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" t="s" s="2">
@@ -45720,14 +45717,14 @@
         <v>269</v>
       </c>
       <c r="L314" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="M314" t="s" s="2">
         <v>885</v>
-      </c>
-      <c r="M314" t="s" s="2">
-        <v>886</v>
       </c>
       <c r="N314" s="2"/>
       <c r="O314" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="P314" t="s" s="2">
         <v>84</v>
@@ -45776,7 +45773,7 @@
         <v>84</v>
       </c>
       <c r="AF314" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AG314" t="s" s="2">
         <v>85</v>
@@ -45815,10 +45812,10 @@
         <v>84</v>
       </c>
       <c r="AS314" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="AT314" t="s" s="2">
         <v>888</v>
-      </c>
-      <c r="AT314" t="s" s="2">
-        <v>889</v>
       </c>
       <c r="AU314" t="s" s="2">
         <v>84</v>
@@ -45826,10 +45823,10 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" t="s" s="2">
@@ -45959,10 +45956,10 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" t="s" s="2">
@@ -46094,10 +46091,10 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" t="s" s="2">
@@ -46123,7 +46120,7 @@
         <v>276</v>
       </c>
       <c r="L317" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M317" t="s" s="2">
         <v>278</v>
@@ -46194,7 +46191,7 @@
         <v>114</v>
       </c>
       <c r="AK317" t="s" s="2">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="AL317" t="s" s="2">
         <v>84</v>
@@ -46229,10 +46226,10 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" t="s" s="2">
@@ -46258,7 +46255,7 @@
         <v>276</v>
       </c>
       <c r="L318" t="s" s="2">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="M318" t="s" s="2">
         <v>288</v>
@@ -46331,7 +46328,7 @@
         <v>114</v>
       </c>
       <c r="AK318" t="s" s="2">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="AL318" t="s" s="2">
         <v>84</v>
@@ -46366,10 +46363,10 @@
     </row>
     <row r="319" hidden="true">
       <c r="A319" t="s" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" t="s" s="2">
@@ -46392,13 +46389,13 @@
         <v>84</v>
       </c>
       <c r="K319" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L319" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="M319" t="s" s="2">
         <v>891</v>
-      </c>
-      <c r="M319" t="s" s="2">
-        <v>892</v>
       </c>
       <c r="N319" s="2"/>
       <c r="O319" s="2"/>
@@ -46449,7 +46446,7 @@
         <v>84</v>
       </c>
       <c r="AF319" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="AG319" t="s" s="2">
         <v>85</v>
@@ -46488,7 +46485,7 @@
         <v>84</v>
       </c>
       <c r="AS319" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AT319" t="s" s="2">
         <v>84</v>
@@ -46499,10 +46496,10 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C320" s="2"/>
       <c r="D320" t="s" s="2">
@@ -46525,19 +46522,19 @@
         <v>84</v>
       </c>
       <c r="K320" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="L320" t="s" s="2">
         <v>1038</v>
       </c>
-      <c r="L320" t="s" s="2">
+      <c r="M320" t="s" s="2">
         <v>1039</v>
       </c>
-      <c r="M320" t="s" s="2">
+      <c r="N320" t="s" s="2">
         <v>1040</v>
       </c>
-      <c r="N320" t="s" s="2">
+      <c r="O320" t="s" s="2">
         <v>1041</v>
-      </c>
-      <c r="O320" t="s" s="2">
-        <v>1042</v>
       </c>
       <c r="P320" t="s" s="2">
         <v>84</v>
@@ -46566,7 +46563,7 @@
       </c>
       <c r="Y320" s="2"/>
       <c r="Z320" t="s" s="2">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="AA320" t="s" s="2">
         <v>84</v>
@@ -46584,7 +46581,7 @@
         <v>84</v>
       </c>
       <c r="AF320" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="AG320" t="s" s="2">
         <v>85</v>
@@ -46620,13 +46617,13 @@
         <v>84</v>
       </c>
       <c r="AR320" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="AS320" t="s" s="2">
         <v>1044</v>
       </c>
-      <c r="AS320" t="s" s="2">
+      <c r="AT320" t="s" s="2">
         <v>1045</v>
-      </c>
-      <c r="AT320" t="s" s="2">
-        <v>1046</v>
       </c>
       <c r="AU320" t="s" s="2">
         <v>84</v>
